--- a/deliverables/06-wrapup/CFU-000-PM-EST-001_Cost-Estimate.xlsx
+++ b/deliverables/06-wrapup/CFU-000-PM-EST-001_Cost-Estimate.xlsx
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57650293.27782979</v>
+        <v>56731775.70104951</v>
       </c>
     </row>
     <row r="3">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>170447511.2309194</v>
+        <v>167817848.0389815</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42611877.80772984</v>
+        <v>41954462.00974537</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>42611877.80772984</v>
+        <v>41954462.00974537</v>
       </c>
     </row>
     <row r="6">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>255671266.846379</v>
+        <v>251726772.0584722</v>
       </c>
     </row>
     <row r="8">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2556.712668463791</v>
+        <v>2517.267720584722</v>
       </c>
     </row>
   </sheetData>
@@ -586,17 +586,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>shell 188 t, 41 trays</t>
+          <t>shell 141 t, 41 trays</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>1.9</v>
       </c>
       <c r="F2" t="n">
-        <v>2737606</v>
+        <v>2317788</v>
       </c>
       <c r="G2" t="n">
-        <v>4212492</v>
+        <v>3566496</v>
       </c>
     </row>
     <row r="3">
@@ -617,17 +617,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>shell 5 t, 6 trays</t>
+          <t>shell 8 t, 6 trays</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>71622</v>
+        <v>93129</v>
       </c>
       <c r="G3" t="n">
-        <v>110208</v>
+        <v>143303</v>
       </c>
     </row>
     <row r="4">
@@ -648,17 +648,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>shell 6 t, 6 trays</t>
+          <t>shell 13 t, 6 trays</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>1.6</v>
       </c>
       <c r="F4" t="n">
-        <v>121935</v>
+        <v>196697</v>
       </c>
       <c r="G4" t="n">
-        <v>187628</v>
+        <v>302668</v>
       </c>
     </row>
     <row r="5">
@@ -679,17 +679,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>shell 4 t, 6 trays</t>
+          <t>shell 9 t, 6 trays</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>1.6</v>
       </c>
       <c r="F5" t="n">
-        <v>91521</v>
+        <v>145599</v>
       </c>
       <c r="G5" t="n">
-        <v>140829</v>
+        <v>224040</v>
       </c>
     </row>
     <row r="6">
@@ -710,17 +710,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>shell 17 t, 19 trays</t>
+          <t>shell 22 t, 19 trays</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>185493</v>
+        <v>216939</v>
       </c>
       <c r="G6" t="n">
-        <v>285427</v>
+        <v>333814</v>
       </c>
     </row>
     <row r="7">
@@ -741,17 +741,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>shell 40 t, 38 trays</t>
+          <t>shell 44 t, 38 trays</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>442299</v>
+        <v>466883</v>
       </c>
       <c r="G7" t="n">
-        <v>680588</v>
+        <v>718416</v>
       </c>
     </row>
     <row r="8">
@@ -772,17 +772,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>shell 155 t, 20 trays, 308 m3 packing</t>
+          <t>shell 160 t, 20 trays, 308 m3 packing</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>1.6</v>
       </c>
       <c r="F8" t="n">
-        <v>4100827</v>
+        <v>4134995</v>
       </c>
       <c r="G8" t="n">
-        <v>6310149</v>
+        <v>6362725</v>
       </c>
     </row>
     <row r="9">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>648 m2, 1 shell(s)</t>
+          <t>84 m2, 1 shell(s)</t>
         </is>
       </c>
       <c r="E26" t="n">
         <v>1.4</v>
       </c>
       <c r="F26" t="n">
-        <v>276430</v>
+        <v>64746</v>
       </c>
       <c r="G26" t="n">
-        <v>425357</v>
+        <v>99627</v>
       </c>
     </row>
     <row r="27">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>117 m2, 1 shell(s)</t>
+          <t>86 m2, 1 shell(s)</t>
         </is>
       </c>
       <c r="E27" t="n">
         <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>53309</v>
+        <v>46698</v>
       </c>
       <c r="G27" t="n">
-        <v>82030</v>
+        <v>71856</v>
       </c>
     </row>
     <row r="28">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>190 m2, 1 shell(s)</t>
+          <t>242 m2, 1 shell(s)</t>
         </is>
       </c>
       <c r="E29" t="n">
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>70000</v>
+        <v>82755</v>
       </c>
       <c r="G29" t="n">
-        <v>107712</v>
+        <v>127340</v>
       </c>
     </row>
     <row r="30">
@@ -1616,10 +1616,10 @@
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>1933952</v>
+        <v>1983952</v>
       </c>
       <c r="G35" t="n">
-        <v>2975869</v>
+        <v>3052806</v>
       </c>
     </row>
     <row r="36">
@@ -1671,17 +1671,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>430 m2 bare</t>
+          <t>302 m2 bare</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>522750</v>
+        <v>382698</v>
       </c>
       <c r="G37" t="n">
-        <v>804382</v>
+        <v>588876</v>
       </c>
     </row>
     <row r="38">
@@ -1771,10 +1771,10 @@
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>1019227</v>
+        <v>1069227</v>
       </c>
       <c r="G40" t="n">
-        <v>1568336</v>
+        <v>1645273</v>
       </c>
     </row>
     <row r="41">
@@ -1857,17 +1857,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>403 m2 bare</t>
+          <t>361 m2 bare</t>
         </is>
       </c>
       <c r="E43" t="n">
         <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>492766</v>
+        <v>447341</v>
       </c>
       <c r="G43" t="n">
-        <v>758244</v>
+        <v>688347</v>
       </c>
     </row>
     <row r="44">
@@ -1888,17 +1888,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>shell 108 t</t>
+          <t>shell 101 t</t>
         </is>
       </c>
       <c r="E44" t="n">
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>1318859</v>
+        <v>1245898</v>
       </c>
       <c r="G44" t="n">
-        <v>2029394</v>
+        <v>1917126</v>
       </c>
     </row>
     <row r="45">
@@ -1919,17 +1919,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>shell 108 t</t>
+          <t>shell 101 t</t>
         </is>
       </c>
       <c r="E45" t="n">
         <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>1318859</v>
+        <v>1245898</v>
       </c>
       <c r="G45" t="n">
-        <v>2029394</v>
+        <v>1917126</v>
       </c>
     </row>
     <row r="46">
@@ -1957,10 +1957,10 @@
         <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>142249</v>
+        <v>142373</v>
       </c>
       <c r="G46" t="n">
-        <v>218886</v>
+        <v>219076</v>
       </c>
     </row>
     <row r="47">
@@ -1988,10 +1988,10 @@
         <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>20289</v>
+        <v>23252</v>
       </c>
       <c r="G47" t="n">
-        <v>31220</v>
+        <v>35779</v>
       </c>
     </row>
     <row r="48">
@@ -2012,17 +2012,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>shell 4 t</t>
+          <t>shell 6 t</t>
         </is>
       </c>
       <c r="E48" t="n">
         <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>46424</v>
+        <v>59403</v>
       </c>
       <c r="G48" t="n">
-        <v>71435</v>
+        <v>91406</v>
       </c>
     </row>
     <row r="49">
@@ -2043,17 +2043,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>shell 9 t</t>
+          <t>shell 8 t</t>
         </is>
       </c>
       <c r="E49" t="n">
         <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>84614</v>
+        <v>77723</v>
       </c>
       <c r="G49" t="n">
-        <v>130200</v>
+        <v>119596</v>
       </c>
     </row>
     <row r="50">
@@ -2081,10 +2081,10 @@
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>32827</v>
+        <v>32014</v>
       </c>
       <c r="G50" t="n">
-        <v>50512</v>
+        <v>49262</v>
       </c>
     </row>
     <row r="51">
@@ -2105,17 +2105,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>shell 0 t</t>
+          <t>shell 1 t</t>
         </is>
       </c>
       <c r="E51" t="n">
         <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>16426</v>
+        <v>19866</v>
       </c>
       <c r="G51" t="n">
-        <v>25276</v>
+        <v>30569</v>
       </c>
     </row>
     <row r="52">
@@ -2136,17 +2136,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>shell 5 t</t>
+          <t>shell 4 t</t>
         </is>
       </c>
       <c r="E52" t="n">
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>54379</v>
+        <v>47405</v>
       </c>
       <c r="G52" t="n">
-        <v>83676</v>
+        <v>72944</v>
       </c>
     </row>
     <row r="53">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2 x 398 m3/h, 250 kW</t>
+          <t>2 x 398 m3/h, 315 kW</t>
         </is>
       </c>
       <c r="E67" t="n">
         <v>1.3</v>
       </c>
       <c r="F67" t="n">
-        <v>173931</v>
+        <v>188392</v>
       </c>
       <c r="G67" t="n">
-        <v>267636</v>
+        <v>289888</v>
       </c>
     </row>
     <row r="68">

--- a/deliverables/06-wrapup/CFU-000-PM-EST-001_Cost-Estimate.xlsx
+++ b/deliverables/06-wrapup/CFU-000-PM-EST-001_Cost-Estimate.xlsx
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>56731775.70104951</v>
+        <v>56791463.43148218</v>
       </c>
     </row>
     <row r="3">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>167817848.0389815</v>
+        <v>168016011.3040179</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41954462.00974537</v>
+        <v>42004002.82600448</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41954462.00974537</v>
+        <v>42004002.82600448</v>
       </c>
     </row>
     <row r="6">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>251726772.0584722</v>
+        <v>252024016.9560269</v>
       </c>
     </row>
     <row r="8">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2517.267720584722</v>
+        <v>2520.240169560269</v>
       </c>
     </row>
   </sheetData>
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2632,17 +2632,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2 x 37 m3/h, 18.5 kW</t>
+          <t>2 x 37 m3/h, 30 kW</t>
         </is>
       </c>
       <c r="E68" t="n">
         <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>42348</v>
+        <v>49207</v>
       </c>
       <c r="G68" t="n">
-        <v>65162</v>
+        <v>75718</v>
       </c>
     </row>
     <row r="69">
@@ -2772,7 +2772,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>P-201A/B</t>
+          <t>P-119A/B</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2782,28 +2782,28 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LVGO pumparound / product</t>
+          <t>Flare KO drum pump-out</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2 x 198 m3/h, 110 kW</t>
+          <t>2 x 21 m3/h, 7.5 kW</t>
         </is>
       </c>
       <c r="E73" t="n">
         <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>111439</v>
+        <v>31930</v>
       </c>
       <c r="G73" t="n">
-        <v>171477</v>
+        <v>49133</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>P-202A/B</t>
+          <t>P-201A/B</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2813,28 +2813,28 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>HVGO pumparound / product</t>
+          <t>LVGO pumparound / product</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2 x 391 m3/h, 200 kW</t>
+          <t>2 x 198 m3/h, 110 kW</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>160933</v>
+        <v>111439</v>
       </c>
       <c r="G74" t="n">
-        <v>247635</v>
+        <v>171477</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>P-203A/B</t>
+          <t>P-202A/B</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2844,28 +2844,28 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Slop wax</t>
+          <t>HVGO pumparound / product</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2 x 12 m3/h, 5.5 kW</t>
+          <t>2 x 391 m3/h, 200 kW</t>
         </is>
       </c>
       <c r="E75" t="n">
         <v>1.3</v>
       </c>
       <c r="F75" t="n">
-        <v>35842</v>
+        <v>160933</v>
       </c>
       <c r="G75" t="n">
-        <v>55152</v>
+        <v>247635</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>P-204A/B</t>
+          <t>P-203A/B</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2875,28 +2875,28 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Vacuum residue (incl. quench)</t>
+          <t>Slop wax</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2 x 196 m3/h, 132 kW</t>
+          <t>2 x 12 m3/h, 5.5 kW</t>
         </is>
       </c>
       <c r="E76" t="n">
         <v>1.3</v>
       </c>
       <c r="F76" t="n">
-        <v>117955</v>
+        <v>35842</v>
       </c>
       <c r="G76" t="n">
-        <v>181504</v>
+        <v>55152</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>P-205A/B</t>
+          <t>P-204A/B</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2906,28 +2906,28 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hotwell sour water</t>
+          <t>Vacuum residue (incl. quench)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2 x 13 m3/h, 3.7 kW</t>
+          <t>2 x 196 m3/h, 132 kW</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="F77" t="n">
-        <v>26952</v>
+        <v>117955</v>
       </c>
       <c r="G77" t="n">
-        <v>41473</v>
+        <v>181504</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>P-206A/B</t>
+          <t>P-205A/B</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2937,59 +2937,59 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hotwell slop oil</t>
+          <t>Hotwell sour water</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2 x 1 m3/h, 0.75 kW</t>
+          <t>2 x 13 m3/h, 3.7 kW</t>
         </is>
       </c>
       <c r="E78" t="n">
         <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>20402</v>
+        <v>26952</v>
       </c>
       <c r="G78" t="n">
-        <v>31393</v>
+        <v>41473</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>X-101</t>
+          <t>P-206A/B</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Pump</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Demulsifier injection package</t>
+          <t>Hotwell slop oil</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>vendor package</t>
+          <t>2 x 1 m3/h, 0.75 kW</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>120000</v>
+        <v>20402</v>
       </c>
       <c r="G79" t="n">
-        <v>184650</v>
+        <v>31393</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>X-102</t>
+          <t>X-101</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Caustic injection package (desalted crude)</t>
+          <t>Demulsifier injection package</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3020,7 +3020,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>X-103</t>
+          <t>X-102</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Neutraliser / filming amine package (atm OH)</t>
+          <t>Caustic injection package (desalted crude)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3051,7 +3051,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>X-104</t>
+          <t>X-103</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Corrosion inhibitor package (VDU OH)</t>
+          <t>Neutraliser / filming amine package (atm OH)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3076,6 +3076,37 @@
         <v>120000</v>
       </c>
       <c r="G82" t="n">
+        <v>184650</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>X-104</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Corrosion inhibitor package (VDU OH)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>vendor package</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F83" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G83" t="n">
         <v>184650</v>
       </c>
     </row>
